--- a/supplementary-material/Supplementary Table S17.xlsx
+++ b/supplementary-material/Supplementary Table S17.xlsx
@@ -3,30 +3,104 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CFC913-79BE-BA4F-9A7D-08BDAD288FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huhuiling/AI_Employment/4 paper：VR WCE/Supplement827/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3EEE96-F7E5-1A42-BFDF-8A7FC18DE0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20780" yWindow="6920" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6380" yWindow="3820" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="segment_extraction_summ" sheetId="1" r:id="rId1"/>
+    <sheet name="kmeans_comparison_summary_segme" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Video</t>
-  </si>
-  <si>
-    <t>FPS</t>
-  </si>
-  <si>
-    <t>Segments</t>
-  </si>
-  <si>
-    <t>segment_extraction_summary</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+  <si>
+    <t>Feature_Setting</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Silhouette_Score</t>
+  </si>
+  <si>
+    <t>Cluster_Sizes</t>
+  </si>
+  <si>
+    <t>N_Segments</t>
+  </si>
+  <si>
+    <t>N_Features_Used</t>
+  </si>
+  <si>
+    <t>PCA_N_Components</t>
+  </si>
+  <si>
+    <t>PCA_Explained_Variance</t>
+  </si>
+  <si>
+    <t>PCA90</t>
+  </si>
+  <si>
+    <t>29199,5096,494</t>
+  </si>
+  <si>
+    <t>5204,29585</t>
+  </si>
+  <si>
+    <t>23378,8058,2859,494</t>
+  </si>
+  <si>
+    <t>9362,20086,1415,3432,494</t>
+  </si>
+  <si>
+    <t>9458,1136,19580,494,3333,788</t>
+  </si>
+  <si>
+    <t>PCA95</t>
+  </si>
+  <si>
+    <t>5088,29207,494</t>
+  </si>
+  <si>
+    <t>5196,29593</t>
+  </si>
+  <si>
+    <t>23431,8027,2837,494</t>
+  </si>
+  <si>
+    <t>3443,20026,9404,494,1422</t>
+  </si>
+  <si>
+    <t>494,9466,3327,772,19598,1132</t>
+  </si>
+  <si>
+    <t>Raw88</t>
+  </si>
+  <si>
+    <t>29210,494,5085</t>
+  </si>
+  <si>
+    <t>29586,5203</t>
+  </si>
+  <si>
+    <t>23455,8023,2817,494</t>
+  </si>
+  <si>
+    <t>9325,1410,20144,494,3416</t>
+  </si>
+  <si>
+    <t>9485,3331,494,19577,772,1130</t>
+  </si>
+  <si>
+    <t>kmeans_comparison_summary_segments</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -199,7 +273,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -209,7 +283,7 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -218,13 +292,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1360,24 +1443,34 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.33203125" style="1"/>
+    <col min="1" max="1" width="14" style="1" customWidth="1"/>
+    <col min="2" max="2" width="2.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+    <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1387,450 +1480,395 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="3">
-        <v>1</v>
+    <row r="3" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="B3" s="4">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.56087126928641895</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>34789</v>
+      </c>
+      <c r="F3" s="5">
+        <v>23</v>
+      </c>
+      <c r="G3" s="5">
+        <v>23</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.90244686104454497</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8">
+        <v>2</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.53947130211564798</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F4" s="9">
+        <v>23</v>
+      </c>
+      <c r="G4" s="9">
+        <v>23</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0.90244686104454497</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="8">
+        <v>4</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.33722245119754801</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F5" s="9">
+        <v>23</v>
+      </c>
+      <c r="G5" s="9">
+        <v>23</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0.90244686104454497</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="8">
+        <v>5</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0.25277976136726499</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F6" s="9">
+        <v>23</v>
+      </c>
+      <c r="G6" s="9">
+        <v>23</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0.90244686104454497</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="8">
+        <v>6</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0.24361541931181399</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F7" s="9">
+        <v>23</v>
+      </c>
+      <c r="G7" s="9">
+        <v>23</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0.90244686104454497</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="8">
+        <v>3</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0.54841204100027796</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F8" s="9">
+        <v>32</v>
+      </c>
+      <c r="G8" s="9">
+        <v>32</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0.95357997250997595</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="8">
+        <v>2</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.52861126069960596</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F9" s="9">
+        <v>32</v>
+      </c>
+      <c r="G9" s="9">
+        <v>32</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0.95357997250997595</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="8">
+        <v>4</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0.32641231899405199</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F10" s="9">
+        <v>32</v>
+      </c>
+      <c r="G10" s="9">
+        <v>32</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0.95357997250997595</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="8">
+        <v>5</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0.23905946836282099</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F11" s="9">
+        <v>32</v>
+      </c>
+      <c r="G11" s="9">
+        <v>32</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0.95357997250997595</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="8">
+        <v>6</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0.23137287957219599</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F12" s="9">
+        <v>32</v>
+      </c>
+      <c r="G12" s="9">
+        <v>32</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0.95357997250997595</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="5">
-        <v>861</v>
-      </c>
+      <c r="B13" s="8">
+        <v>3</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0.53854128749629604</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F13" s="9">
+        <v>88</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
     </row>
-    <row r="4" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="6">
+    <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="8">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
+      <c r="C14" s="9">
+        <v>0.52001138755082699</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F14" s="9">
+        <v>88</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="8">
-        <v>871</v>
-      </c>
+      <c r="B15" s="8">
+        <v>4</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0.31733880376818502</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F15" s="9">
+        <v>88</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
     </row>
-    <row r="5" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="6">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7">
+    <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="8">
-        <v>862</v>
-      </c>
+      <c r="B16" s="8">
+        <v>5</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0.23180710289367801</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F16" s="9">
+        <v>88</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
     </row>
-    <row r="6" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7">
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="8">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="6">
+      <c r="B17" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="7">
-        <v>20</v>
-      </c>
-      <c r="C7" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7">
-        <v>20</v>
-      </c>
-      <c r="C8" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7">
-        <v>20</v>
-      </c>
-      <c r="C9" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7">
-        <v>20</v>
-      </c>
-      <c r="C11" s="8">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="6">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7">
-        <v>20</v>
-      </c>
-      <c r="C12" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="6">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7">
-        <v>20</v>
-      </c>
-      <c r="C13" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="6">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7">
-        <v>20</v>
-      </c>
-      <c r="C14" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="6">
-        <v>14</v>
-      </c>
-      <c r="B15" s="7">
-        <v>20</v>
-      </c>
-      <c r="C15" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="6">
-        <v>15</v>
-      </c>
-      <c r="B16" s="7">
-        <v>20</v>
-      </c>
-      <c r="C16" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="6">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7">
-        <v>20</v>
-      </c>
-      <c r="C17" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="6">
-        <v>17</v>
-      </c>
-      <c r="B18" s="7">
-        <v>20</v>
-      </c>
-      <c r="C18" s="8">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="6">
-        <v>18</v>
-      </c>
-      <c r="B19" s="7">
-        <v>20</v>
-      </c>
-      <c r="C19" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="6">
-        <v>19</v>
-      </c>
-      <c r="B20" s="7">
-        <v>15</v>
-      </c>
-      <c r="C20" s="8">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="6">
-        <v>90</v>
-      </c>
-      <c r="B21" s="7">
-        <v>20</v>
-      </c>
-      <c r="C21" s="8">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="6">
-        <v>91</v>
-      </c>
-      <c r="B22" s="7">
-        <v>20</v>
-      </c>
-      <c r="C22" s="8">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="6">
-        <v>92</v>
-      </c>
-      <c r="B23" s="7">
-        <v>20</v>
-      </c>
-      <c r="C23" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="6">
-        <v>93</v>
-      </c>
-      <c r="B24" s="7">
-        <v>20</v>
-      </c>
-      <c r="C24" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="6">
-        <v>94</v>
-      </c>
-      <c r="B25" s="7">
-        <v>20</v>
-      </c>
-      <c r="C25" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="6">
-        <v>95</v>
-      </c>
-      <c r="B26" s="7">
-        <v>20</v>
-      </c>
-      <c r="C26" s="8">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="6">
-        <v>96</v>
-      </c>
-      <c r="B27" s="7">
-        <v>20</v>
-      </c>
-      <c r="C27" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="6">
-        <v>97</v>
-      </c>
-      <c r="B28" s="7">
-        <v>20</v>
-      </c>
-      <c r="C28" s="8">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="6">
-        <v>98</v>
-      </c>
-      <c r="B29" s="7">
-        <v>20</v>
-      </c>
-      <c r="C29" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="6">
-        <v>99</v>
-      </c>
-      <c r="B30" s="7">
-        <v>20</v>
-      </c>
-      <c r="C30" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="6">
-        <v>100</v>
-      </c>
-      <c r="B31" s="7">
-        <v>20</v>
-      </c>
-      <c r="C31" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="6">
-        <v>101</v>
-      </c>
-      <c r="B32" s="7">
-        <v>20</v>
-      </c>
-      <c r="C32" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="6">
-        <v>102</v>
-      </c>
-      <c r="B33" s="7">
-        <v>20</v>
-      </c>
-      <c r="C33" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="6">
-        <v>103</v>
-      </c>
-      <c r="B34" s="7">
-        <v>20</v>
-      </c>
-      <c r="C34" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="6">
-        <v>104</v>
-      </c>
-      <c r="B35" s="7">
-        <v>20</v>
-      </c>
-      <c r="C35" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="6">
-        <v>105</v>
-      </c>
-      <c r="B36" s="7">
-        <v>20</v>
-      </c>
-      <c r="C36" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="6">
-        <v>106</v>
-      </c>
-      <c r="B37" s="7">
-        <v>20</v>
-      </c>
-      <c r="C37" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="6">
-        <v>107</v>
-      </c>
-      <c r="B38" s="7">
-        <v>20</v>
-      </c>
-      <c r="C38" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="6">
-        <v>108</v>
-      </c>
-      <c r="B39" s="7">
-        <v>20</v>
-      </c>
-      <c r="C39" s="8">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="6">
-        <v>109</v>
-      </c>
-      <c r="B40" s="7">
-        <v>20</v>
-      </c>
-      <c r="C40" s="8">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="6">
-        <v>110</v>
-      </c>
-      <c r="B41" s="7">
-        <v>20</v>
-      </c>
-      <c r="C41" s="8">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="6">
-        <v>111</v>
-      </c>
-      <c r="B42" s="7">
-        <v>20</v>
-      </c>
-      <c r="C42" s="8">
-        <v>863</v>
-      </c>
+      <c r="C17" s="9">
+        <v>0.22174715627813699</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="9">
+        <v>34789</v>
+      </c>
+      <c r="F17" s="9">
+        <v>88</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
